--- a/diss/np.xlsx
+++ b/diss/np.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\PVT_TSU\diss\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C455BEA-6A9E-4986-A4E4-A62DB32AB7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CEDE27E-F560-4B19-BD40-BD0745975E17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="17640" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="to_model" sheetId="1" r:id="rId1"/>
+    <sheet name="Лист1" sheetId="2" r:id="rId2"/>
+    <sheet name="to_model_36comps_shlm" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="63">
   <si>
     <t>CO2</t>
   </si>
@@ -88,6 +90,141 @@
   </si>
   <si>
     <t>value</t>
+  </si>
+  <si>
+    <t>N2</t>
+  </si>
+  <si>
+    <t>i-C4</t>
+  </si>
+  <si>
+    <t>n-C4</t>
+  </si>
+  <si>
+    <t>i-C5</t>
+  </si>
+  <si>
+    <t>n-C5</t>
+  </si>
+  <si>
+    <t>Mcyclo-C5</t>
+  </si>
+  <si>
+    <t>Метилциклопентан</t>
+  </si>
+  <si>
+    <t>Benzene</t>
+  </si>
+  <si>
+    <t>Бензол</t>
+  </si>
+  <si>
+    <t>Cyclo-C6</t>
+  </si>
+  <si>
+    <t>Циклогексан</t>
+  </si>
+  <si>
+    <t>Mcyclo-C6</t>
+  </si>
+  <si>
+    <t>Метилциклогексан</t>
+  </si>
+  <si>
+    <t>Toluene</t>
+  </si>
+  <si>
+    <t>Толуол</t>
+  </si>
+  <si>
+    <t>C2-Benzene</t>
+  </si>
+  <si>
+    <t>С2-Бензол</t>
+  </si>
+  <si>
+    <t>m&amp;p-Xylene</t>
+  </si>
+  <si>
+    <t>м,п-Ксилол</t>
+  </si>
+  <si>
+    <t>o-Xylene</t>
+  </si>
+  <si>
+    <t>о-Ксилол</t>
+  </si>
+  <si>
+    <t>C14</t>
+  </si>
+  <si>
+    <t>C15</t>
+  </si>
+  <si>
+    <t>C16</t>
+  </si>
+  <si>
+    <t>C17</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
+    <t>C24</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C35</t>
+  </si>
+  <si>
+    <t>C36+</t>
+  </si>
+  <si>
+    <t>C36</t>
   </si>
 </sst>
 </file>
@@ -103,12 +240,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -123,8 +278,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -550,4 +711,931 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0392062-D225-47A3-80BB-71F869AA3484}">
+  <dimension ref="A1:E48"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="E1">
+        <f>C1/100</f>
+        <v>1.4499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2">
+        <v>6.2E-2</v>
+      </c>
+      <c r="E2">
+        <f t="shared" ref="E2:E9" si="0">C2/100</f>
+        <v>6.2E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>42.011000000000003</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="0"/>
+        <v>0.42011000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>4.5780000000000003</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="0"/>
+        <v>4.5780000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>3.5379999999999998</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>3.5379999999999995E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6">
+        <v>1.034</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>1.034E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>1.635</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="0"/>
+        <v>1.635E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C8">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>8.5699999999999995E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9">
+        <v>0.87</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="0"/>
+        <v>8.6999999999999994E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1">
+        <v>1.524</v>
+      </c>
+      <c r="D10" s="4">
+        <f>SUM(C10:C13)</f>
+        <v>3.3359999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="1">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="1">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1">
+        <v>0.95099999999999996</v>
+      </c>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2">
+        <v>1.6180000000000001</v>
+      </c>
+      <c r="D14" s="4">
+        <f>SUM(C14:C16)</f>
+        <v>4.569</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" s="2">
+        <v>2.153</v>
+      </c>
+      <c r="D15" s="4"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C16" s="2">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="D16" s="4"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3">
+        <v>2.294</v>
+      </c>
+      <c r="D17" s="4">
+        <f>SUM(C17:C20)</f>
+        <v>4.1869999999999994</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="3">
+        <v>0.193</v>
+      </c>
+      <c r="D18" s="4"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="3">
+        <v>1.39</v>
+      </c>
+      <c r="D19" s="4"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="3">
+        <v>0.31</v>
+      </c>
+      <c r="D20" s="4"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21">
+        <v>1.8</v>
+      </c>
+      <c r="E21">
+        <f t="shared" ref="E21:E48" si="1">C21/100</f>
+        <v>1.8000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22">
+        <v>2.9590000000000001</v>
+      </c>
+      <c r="E22">
+        <f t="shared" si="1"/>
+        <v>2.9590000000000002E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23">
+        <v>2.3170000000000002</v>
+      </c>
+      <c r="E23">
+        <f t="shared" si="1"/>
+        <v>2.3170000000000003E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24">
+        <v>2.3119999999999998</v>
+      </c>
+      <c r="E24">
+        <f t="shared" si="1"/>
+        <v>2.3119999999999998E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25">
+        <v>2.6019999999999999</v>
+      </c>
+      <c r="E25">
+        <f t="shared" si="1"/>
+        <v>2.6019999999999998E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26">
+        <v>2.3250000000000002</v>
+      </c>
+      <c r="E26">
+        <f t="shared" si="1"/>
+        <v>2.3250000000000003E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27">
+        <v>2.552</v>
+      </c>
+      <c r="E27">
+        <f t="shared" si="1"/>
+        <v>2.5520000000000001E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28">
+        <v>2.0350000000000001</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="1"/>
+        <v>2.035E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29">
+        <v>1.776</v>
+      </c>
+      <c r="E29">
+        <f t="shared" si="1"/>
+        <v>1.7760000000000001E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30">
+        <v>1.6919999999999999</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="1"/>
+        <v>1.6920000000000001E-2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31">
+        <v>1.4039999999999999</v>
+      </c>
+      <c r="E31">
+        <f t="shared" si="1"/>
+        <v>1.4039999999999999E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32">
+        <v>1.1220000000000001</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="1"/>
+        <v>1.1220000000000001E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33">
+        <v>0.96</v>
+      </c>
+      <c r="E33">
+        <f t="shared" si="1"/>
+        <v>9.5999999999999992E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="E34">
+        <f t="shared" si="1"/>
+        <v>8.1599999999999989E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="E35">
+        <f t="shared" si="1"/>
+        <v>6.8700000000000002E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>49</v>
+      </c>
+      <c r="C36">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="E36">
+        <f t="shared" si="1"/>
+        <v>5.8599999999999998E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37">
+        <v>0.503</v>
+      </c>
+      <c r="E37">
+        <f t="shared" si="1"/>
+        <v>5.0299999999999997E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>51</v>
+      </c>
+      <c r="C38">
+        <v>0.42799999999999999</v>
+      </c>
+      <c r="E38">
+        <f t="shared" si="1"/>
+        <v>4.28E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="C39">
+        <v>0.372</v>
+      </c>
+      <c r="E39">
+        <f t="shared" si="1"/>
+        <v>3.7199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40">
+        <v>0.32</v>
+      </c>
+      <c r="E40">
+        <f t="shared" si="1"/>
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="1"/>
+        <v>2.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42">
+        <v>0.252</v>
+      </c>
+      <c r="E42">
+        <f t="shared" si="1"/>
+        <v>2.5200000000000001E-3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>56</v>
+      </c>
+      <c r="C43">
+        <v>0.22600000000000001</v>
+      </c>
+      <c r="E43">
+        <f t="shared" si="1"/>
+        <v>2.2599999999999999E-3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>57</v>
+      </c>
+      <c r="C44">
+        <v>0.19400000000000001</v>
+      </c>
+      <c r="E44">
+        <f t="shared" si="1"/>
+        <v>1.9400000000000001E-3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>58</v>
+      </c>
+      <c r="C45">
+        <v>0.17799999999999999</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="1"/>
+        <v>1.7799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46">
+        <v>0.16</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="1"/>
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>60</v>
+      </c>
+      <c r="C47">
+        <v>0.14499999999999999</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="1"/>
+        <v>1.4499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>61</v>
+      </c>
+      <c r="C48">
+        <v>2.165</v>
+      </c>
+      <c r="E48">
+        <f t="shared" si="1"/>
+        <v>2.1649999999999999E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="D10:D13"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="D17:D20"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA6A0E49-660D-4DF2-A046-0CF9F1C5189B}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>1.4499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2">
+        <v>6.2E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>0.42011000000000004</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>4.5780000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3.5379999999999995E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>1.034E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>1.635E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8">
+        <v>8.5699999999999995E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9">
+        <v>8.6999999999999994E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>3.3360000000000001E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>4.5690000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>4.1869999999999991E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13">
+        <v>1.8000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>2.9590000000000002E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>2.3170000000000003E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16">
+        <v>2.3119999999999998E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>2.6019999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18">
+        <v>2.3250000000000003E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19">
+        <v>2.5520000000000001E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20">
+        <v>2.035E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21">
+        <v>1.7760000000000001E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22">
+        <v>1.6920000000000001E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23">
+        <v>1.4039999999999999E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24">
+        <v>1.1220000000000001E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B25">
+        <v>9.5999999999999992E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26">
+        <v>8.1599999999999989E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27">
+        <v>6.8700000000000002E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="B28">
+        <v>5.8599999999999998E-3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="B29">
+        <v>5.0299999999999997E-3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30">
+        <v>4.28E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31">
+        <v>3.7199999999999998E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B32">
+        <v>3.2000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="B33">
+        <v>2.9199999999999999E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34">
+        <v>2.5200000000000001E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35">
+        <v>2.2599999999999999E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36">
+        <v>1.9400000000000001E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37">
+        <v>1.7799999999999999E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>59</v>
+      </c>
+      <c r="B38">
+        <v>1.6000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>60</v>
+      </c>
+      <c r="B39">
+        <v>1.4499999999999999E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>62</v>
+      </c>
+      <c r="B40">
+        <v>2.1649999999999999E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>